--- a/excel/28 - Formula Excel Template.xlsx
+++ b/excel/28 - Formula Excel Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dan\source\repos\Data-Analyst-Bootcamp\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB9596C-FC91-48AD-96D7-DBC0E2A4E9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8D259C-4F66-41F2-BC3A-71AFD16BE090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="10" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Max-Min" sheetId="9" r:id="rId1"/>
@@ -45,8 +45,9 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -57,11 +58,25 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
@@ -390,6 +405,64 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>13</v>
+    <v>24</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1094,6 +1167,18 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2">
+        <f>COUNT(G2:G10)</f>
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <f>COUNTIF(G2:G10, "&gt;50000")</f>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <f>COUNTIFS( E2:E10, "Male", D2:D10, "&gt;30")</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -1406,6 +1491,14 @@
       </c>
       <c r="I2" s="2" t="s">
         <v>56</v>
+      </c>
+      <c r="J2" t="e" vm="1">
+        <f>_xleta.DAYS</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K2" t="e" cm="1">
+        <f t="array" ref="K2">NETWO</f>
+        <v>#NAME?</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -3955,6 +4048,14 @@
       <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J10">SUBSTITUTE(H2:H10, "/", "-", 1)</f>
+        <v>11-2/2001</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:L10">SUBSTITUTE(H2:H10, "/", "-")</f>
+        <v>11-2-2001</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -3984,6 +4085,12 @@
       <c r="I3" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="J3" t="str">
+        <v>10-3/1999</v>
+      </c>
+      <c r="L3" t="str">
+        <v>10-3-1999</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -4013,6 +4120,12 @@
       <c r="I4" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="J4" t="str">
+        <v>7-4/2000</v>
+      </c>
+      <c r="L4" t="str">
+        <v>7-4-2000</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -4042,6 +4155,12 @@
       <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="J5" t="str">
+        <v>1-5/2000</v>
+      </c>
+      <c r="L5" t="str">
+        <v>1-5-2000</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -4071,6 +4190,12 @@
       <c r="I6" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="J6" t="str">
+        <v>5-6/2001</v>
+      </c>
+      <c r="L6" t="str">
+        <v>5-6-2001</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -4100,6 +4225,12 @@
       <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J7" t="str">
+        <v>5-6/2001</v>
+      </c>
+      <c r="L7" t="str">
+        <v>5-6-2001</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -4129,6 +4260,12 @@
       <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J8" t="str">
+        <v>11-8/2003</v>
+      </c>
+      <c r="L8" t="str">
+        <v>11-8-2003</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -4158,6 +4295,12 @@
       <c r="I9" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="J9" t="str">
+        <v>6-9/2002</v>
+      </c>
+      <c r="L9" t="str">
+        <v>6-9-2002</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -4186,6 +4329,12 @@
       </c>
       <c r="I10" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="J10" t="str">
+        <v>8-10/2003</v>
+      </c>
+      <c r="L10" t="str">
+        <v>8-10-2003</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -4304,6 +4453,18 @@
       <c r="I2" s="1">
         <v>42253</v>
       </c>
+      <c r="J2">
+        <f>SUM(G2:G10)</f>
+        <v>437000</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF(G2:G10, "&gt;50000")</f>
+        <v>128000</v>
+      </c>
+      <c r="L2">
+        <f>SUMIFS(G2:G10, E2:E10, "Female",D2:D10, "&gt;30")</f>
+        <v>88000</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">

--- a/excel/28 - Formula Excel Template.xlsx
+++ b/excel/28 - Formula Excel Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dan\source\repos\Data-Analyst-Bootcamp\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8D259C-4F66-41F2-BC3A-71AFD16BE090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78290A7B-877D-403E-BE97-19674915739F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="10" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
   </bookViews>
@@ -45,9 +45,8 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
+  <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -58,25 +57,11 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </valueMetadata>
 </metadata>
 </file>
 
@@ -405,64 +390,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>13</v>
-    <v>24</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1492,13 +1419,13 @@
       <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J2" t="e" vm="1">
-        <f>_xleta.DAYS</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K2" t="e" cm="1">
-        <f t="array" ref="K2">NETWO</f>
-        <v>#NAME?</v>
+      <c r="J2">
+        <f>_xlfn.DAYS(I2,H2)</f>
+        <v>5056</v>
+      </c>
+      <c r="K2">
+        <f>NETWORKDAYS(H2,I2)</f>
+        <v>3611</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1529,6 +1456,14 @@
       <c r="I3" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J10" si="0">_xlfn.DAYS(I3,H3)</f>
+        <v>5851</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K10" si="1">NETWORKDAYS(H3,I3)</f>
+        <v>4180</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -1558,6 +1493,14 @@
       <c r="I4" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>6275</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>4484</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -1587,6 +1530,14 @@
       <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>5811</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>4152</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -1616,6 +1567,14 @@
       <c r="I6" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>5960</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>4258</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -1645,6 +1604,14 @@
       <c r="I7" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>4511</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>3223</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -1674,6 +1641,14 @@
       <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>3595</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>2568</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1703,6 +1678,14 @@
       <c r="I9" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>4700</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>3358</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -1731,6 +1714,14 @@
       </c>
       <c r="I10" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>4273</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>3053</v>
       </c>
     </row>
   </sheetData>
